--- a/SNK06D.xlsx
+++ b/SNK06D.xlsx
@@ -64,7 +64,7 @@
     <t>20094328</t>
   </si>
   <si>
-    <t>PIATTOS SMB GPREK 68</t>
+    <t>PIATTOS SMB GPREK 65</t>
   </si>
   <si>
     <t>5</t>
@@ -115,7 +115,7 @@
     <t>20025762</t>
   </si>
   <si>
-    <t>PIATTOS SAPI PNG 68G</t>
+    <t>PIATTOS SAPI PNG 65G</t>
   </si>
   <si>
     <t>20138228</t>
@@ -3862,7 +3862,7 @@
         <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>139</v>
@@ -3882,7 +3882,7 @@
         <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>37</v>
@@ -3902,7 +3902,7 @@
         <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>37</v>
